--- a/temp.xlsx
+++ b/temp.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +620,462 @@
         <v>12</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46019.78710940972</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46019.78725230324</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46019.78739605324</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46019.78754708333</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46019.78770908565</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46019.7878722801</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46019.78803903935</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46019.78819797454</v>
+      </c>
+      <c r="B31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46019.78837785879</v>
+      </c>
+      <c r="B32" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46019.78855489584</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46019.788728125</v>
+      </c>
+      <c r="B34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46019.78890439815</v>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46019.78909473379</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46019.78927900463</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46019.78945652777</v>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46019.78962299768</v>
+      </c>
+      <c r="B39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46019.79917954861</v>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46019.79933003472</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46019.79948458333</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46019.79964241898</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46019.79980773148</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46019.79997678241</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46019.80014923611</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46019.80032202546</v>
+      </c>
+      <c r="B47" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46019.80050456018</v>
+      </c>
+      <c r="B48" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46019.80069651621</v>
+      </c>
+      <c r="B49" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46019.80088616898</v>
+      </c>
+      <c r="B50" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46019.80106292824</v>
+      </c>
+      <c r="B51" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46019.80124872685</v>
+      </c>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46019.80143684028</v>
+      </c>
+      <c r="B53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46019.80161681713</v>
+      </c>
+      <c r="B54" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46019.8017946412</v>
+      </c>
+      <c r="B55" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46019.80630458333</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46019.80639174768</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46019.80648799769</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46019.80657899306</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46019.80667068287</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46019.8067622338</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46019.80685096065</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46019.80694037037</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46019.80702836806</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46019.80712328704</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46019.80722640047</v>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46019.80732671297</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46019.80742377315</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46019.8671515625</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46019.86730526621</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46019.86745759259</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46019.86760027778</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46019.86774581019</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46019.86789157407</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46019.86804280092</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46019.86819030093</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46019.86834508102</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46019.86854447917</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46019.86981938657</v>
+      </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46019.87001287037</v>
+      </c>
+      <c r="B80" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/temp.xlsx
+++ b/temp.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,135 +446,135 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46014.9239386574</v>
+        <v>46017.03108173611</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46014.92414760416</v>
+        <v>46017.03802618055</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46014.92435851852</v>
+        <v>46017.044970625</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46014.9245669213</v>
+        <v>46017.05191506945</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46014.92476284722</v>
+        <v>46017.05885951389</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46014.92497251157</v>
+        <v>46017.06580395834</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46014.93146513889</v>
+        <v>46017.07274840278</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46014.93161486111</v>
+        <v>46017.07969284722</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46014.93177474537</v>
+        <v>46017.08663729166</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46014.93192842593</v>
+        <v>46017.09358173611</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46014.93208961806</v>
+        <v>46017.10052618055</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46014.93227585648</v>
+        <v>46017.107470625</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46014.93244497685</v>
+        <v>46017.11441506945</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46014.93260789352</v>
+        <v>46017.12135951389</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46014.932790625</v>
+        <v>46017.12830395834</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46014.93298600694</v>
+        <v>46017.13524840278</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46014.93316688657</v>
+        <v>46017.14219284722</v>
       </c>
       <c r="B18" t="n">
         <v>11</v>
@@ -582,151 +582,151 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46014.93334972223</v>
+        <v>46017.14913729166</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46014.9335396875</v>
+        <v>46017.15608173611</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46014.9337271412</v>
+        <v>46017.16302618055</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46014.93390376157</v>
+        <v>46017.169970625</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46014.93407923611</v>
+        <v>46017.17691506945</v>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46019.78710940972</v>
+        <v>46017.18385951389</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46019.78725230324</v>
+        <v>46017.19080395834</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46019.78739605324</v>
+        <v>46017.19774840278</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46019.78754708333</v>
+        <v>46017.20469284722</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46019.78770908565</v>
+        <v>46017.21163729166</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46019.7878722801</v>
+        <v>46017.21858173611</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46019.78803903935</v>
+        <v>46017.22552618055</v>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46019.78819797454</v>
+        <v>46017.232470625</v>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46019.78837785879</v>
+        <v>46017.23941506945</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46019.78855489584</v>
+        <v>46017.24635951389</v>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46019.788728125</v>
+        <v>46017.25330395834</v>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46019.78890439815</v>
+        <v>46017.26024840278</v>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46019.78909473379</v>
+        <v>46017.26719284722</v>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46019.78927900463</v>
+        <v>46017.27413729166</v>
       </c>
       <c r="B37" t="n">
         <v>10</v>
@@ -734,346 +734,3714 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46019.78945652777</v>
+        <v>46017.28108173611</v>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46019.78962299768</v>
+        <v>46017.28802618055</v>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46019.79917954861</v>
+        <v>46017.294970625</v>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46019.79933003472</v>
+        <v>46017.30191506945</v>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46019.79948458333</v>
+        <v>46017.30885951389</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46019.79964241898</v>
+        <v>46017.31580395834</v>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46019.79980773148</v>
+        <v>46017.32274840278</v>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46019.79997678241</v>
+        <v>46017.32969284722</v>
       </c>
       <c r="B45" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46019.80014923611</v>
+        <v>46017.33663729166</v>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46019.80032202546</v>
+        <v>46017.34358173611</v>
       </c>
       <c r="B47" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46019.80050456018</v>
+        <v>46017.35052618055</v>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46019.80069651621</v>
+        <v>46017.357470625</v>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46019.80088616898</v>
+        <v>46017.36441506945</v>
       </c>
       <c r="B50" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46019.80106292824</v>
+        <v>46017.37135951389</v>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46019.80124872685</v>
+        <v>46017.37830395834</v>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46019.80143684028</v>
+        <v>46017.38524840278</v>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46019.80161681713</v>
+        <v>46017.39219284722</v>
       </c>
       <c r="B54" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46019.8017946412</v>
+        <v>46017.39913729166</v>
       </c>
       <c r="B55" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46019.80630458333</v>
+        <v>46017.40608173611</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46019.80639174768</v>
+        <v>46017.41302618055</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46019.80648799769</v>
+        <v>46017.419970625</v>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46019.80657899306</v>
+        <v>46017.42691506945</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46019.80667068287</v>
+        <v>46017.43385951389</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46019.8067622338</v>
+        <v>46017.44080395834</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46019.80685096065</v>
+        <v>46017.44774840278</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46019.80694037037</v>
+        <v>46017.45469284722</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46019.80702836806</v>
+        <v>46017.46163729166</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46019.80712328704</v>
+        <v>46017.46858173611</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46019.80722640047</v>
+        <v>46017.47552618055</v>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46019.80732671297</v>
+        <v>46017.482470625</v>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46019.80742377315</v>
+        <v>46017.48941506945</v>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46019.8671515625</v>
+        <v>46017.49635951389</v>
       </c>
       <c r="B69" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46019.86730526621</v>
+        <v>46017.50330395834</v>
       </c>
       <c r="B70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46019.86745759259</v>
+        <v>46017.51024840278</v>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46019.86760027778</v>
+        <v>46017.51719284722</v>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46019.86774581019</v>
+        <v>46017.52413729166</v>
       </c>
       <c r="B73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46019.86789157407</v>
+        <v>46017.53108173611</v>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46019.86804280092</v>
+        <v>46017.53802618055</v>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46019.86819030093</v>
+        <v>46017.544970625</v>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46019.86834508102</v>
+        <v>46017.55191506945</v>
       </c>
       <c r="B77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46019.86854447917</v>
+        <v>46017.55885951389</v>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46019.86981938657</v>
+        <v>46017.56580395834</v>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
+        <v>46017.57274840278</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46017.57969284722</v>
+      </c>
+      <c r="B81" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46017.58663729166</v>
+      </c>
+      <c r="B82" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46017.59358173611</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46017.60052618055</v>
+      </c>
+      <c r="B84" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46017.607470625</v>
+      </c>
+      <c r="B85" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46017.61441506945</v>
+      </c>
+      <c r="B86" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46017.62135951389</v>
+      </c>
+      <c r="B87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46017.62830395834</v>
+      </c>
+      <c r="B88" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46017.63524840278</v>
+      </c>
+      <c r="B89" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46017.64219284722</v>
+      </c>
+      <c r="B90" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46017.64913729166</v>
+      </c>
+      <c r="B91" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46017.65608173611</v>
+      </c>
+      <c r="B92" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46017.66302618055</v>
+      </c>
+      <c r="B93" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46017.669970625</v>
+      </c>
+      <c r="B94" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46017.67691506945</v>
+      </c>
+      <c r="B95" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46017.68385951389</v>
+      </c>
+      <c r="B96" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46017.69080395834</v>
+      </c>
+      <c r="B97" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46017.69774840278</v>
+      </c>
+      <c r="B98" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46017.70469284722</v>
+      </c>
+      <c r="B99" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46017.71163729166</v>
+      </c>
+      <c r="B100" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46017.71858173611</v>
+      </c>
+      <c r="B101" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46017.72552618055</v>
+      </c>
+      <c r="B102" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46017.732470625</v>
+      </c>
+      <c r="B103" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46017.73941506945</v>
+      </c>
+      <c r="B104" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46017.74635951389</v>
+      </c>
+      <c r="B105" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46017.75330395834</v>
+      </c>
+      <c r="B106" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46017.76024840278</v>
+      </c>
+      <c r="B107" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46017.76719284722</v>
+      </c>
+      <c r="B108" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46017.77413729166</v>
+      </c>
+      <c r="B109" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46017.78108173611</v>
+      </c>
+      <c r="B110" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46017.78802618055</v>
+      </c>
+      <c r="B111" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46017.794970625</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46017.80191506945</v>
+      </c>
+      <c r="B113" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46017.80885951389</v>
+      </c>
+      <c r="B114" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46017.81580395834</v>
+      </c>
+      <c r="B115" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46017.82274840278</v>
+      </c>
+      <c r="B116" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46017.82969284722</v>
+      </c>
+      <c r="B117" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46017.83663729166</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46017.84358173611</v>
+      </c>
+      <c r="B119" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46017.85052618055</v>
+      </c>
+      <c r="B120" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46017.857470625</v>
+      </c>
+      <c r="B121" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46017.86441506945</v>
+      </c>
+      <c r="B122" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46017.87135951389</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46017.87830395834</v>
+      </c>
+      <c r="B124" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46017.88524840278</v>
+      </c>
+      <c r="B125" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46017.89219284722</v>
+      </c>
+      <c r="B126" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46017.89913729166</v>
+      </c>
+      <c r="B127" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46017.90608173611</v>
+      </c>
+      <c r="B128" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46017.91302618055</v>
+      </c>
+      <c r="B129" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46017.919970625</v>
+      </c>
+      <c r="B130" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46017.92691506945</v>
+      </c>
+      <c r="B131" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46017.93385951389</v>
+      </c>
+      <c r="B132" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46017.94080395834</v>
+      </c>
+      <c r="B133" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46017.94774840278</v>
+      </c>
+      <c r="B134" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46017.95469284722</v>
+      </c>
+      <c r="B135" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46017.96163729166</v>
+      </c>
+      <c r="B136" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46017.96858173611</v>
+      </c>
+      <c r="B137" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46017.97552618055</v>
+      </c>
+      <c r="B138" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46017.982470625</v>
+      </c>
+      <c r="B139" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46017.98941506945</v>
+      </c>
+      <c r="B140" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46017.99635951389</v>
+      </c>
+      <c r="B141" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46018.00330395834</v>
+      </c>
+      <c r="B142" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46018.01024840278</v>
+      </c>
+      <c r="B143" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46018.01719284722</v>
+      </c>
+      <c r="B144" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46018.02413729166</v>
+      </c>
+      <c r="B145" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46018.03108173611</v>
+      </c>
+      <c r="B146" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46018.03802618055</v>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46018.044970625</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46018.05191506945</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46018.05885951389</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46018.06580395834</v>
+      </c>
+      <c r="B151" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46018.07274840278</v>
+      </c>
+      <c r="B152" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46018.07969284722</v>
+      </c>
+      <c r="B153" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46018.08663729166</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46018.09358173611</v>
+      </c>
+      <c r="B155" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46018.10052618055</v>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46018.107470625</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46018.11441506945</v>
+      </c>
+      <c r="B158" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46018.12135951389</v>
+      </c>
+      <c r="B159" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46018.12830395834</v>
+      </c>
+      <c r="B160" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46018.13524840278</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46018.14219284722</v>
+      </c>
+      <c r="B162" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46018.14913729166</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46018.15608173611</v>
+      </c>
+      <c r="B164" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46018.16302618055</v>
+      </c>
+      <c r="B165" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46018.169970625</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46018.17691506945</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46018.18385951389</v>
+      </c>
+      <c r="B168" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46018.19080395834</v>
+      </c>
+      <c r="B169" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46018.19774840278</v>
+      </c>
+      <c r="B170" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46018.20469284722</v>
+      </c>
+      <c r="B171" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46018.21163729166</v>
+      </c>
+      <c r="B172" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46018.21858173611</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46018.22552618055</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46018.232470625</v>
+      </c>
+      <c r="B175" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46018.23941506945</v>
+      </c>
+      <c r="B176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46018.24635951389</v>
+      </c>
+      <c r="B177" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46018.25330395834</v>
+      </c>
+      <c r="B178" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46018.26024840278</v>
+      </c>
+      <c r="B179" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46018.26719284722</v>
+      </c>
+      <c r="B180" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46018.27413729166</v>
+      </c>
+      <c r="B181" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46018.28108173611</v>
+      </c>
+      <c r="B182" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46018.28802618055</v>
+      </c>
+      <c r="B183" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46018.294970625</v>
+      </c>
+      <c r="B184" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46018.30191506945</v>
+      </c>
+      <c r="B185" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46018.30885951389</v>
+      </c>
+      <c r="B186" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46018.31580395834</v>
+      </c>
+      <c r="B187" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46018.32274840278</v>
+      </c>
+      <c r="B188" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46018.32969284722</v>
+      </c>
+      <c r="B189" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46018.33663729166</v>
+      </c>
+      <c r="B190" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46018.34358173611</v>
+      </c>
+      <c r="B191" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46018.35052618055</v>
+      </c>
+      <c r="B192" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46018.357470625</v>
+      </c>
+      <c r="B193" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46018.36441506945</v>
+      </c>
+      <c r="B194" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46018.37135951389</v>
+      </c>
+      <c r="B195" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46018.37830395834</v>
+      </c>
+      <c r="B196" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46018.38524840278</v>
+      </c>
+      <c r="B197" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46018.39219284722</v>
+      </c>
+      <c r="B198" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46018.39913729166</v>
+      </c>
+      <c r="B199" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46018.40608173611</v>
+      </c>
+      <c r="B200" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46018.41302618055</v>
+      </c>
+      <c r="B201" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46018.419970625</v>
+      </c>
+      <c r="B202" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46018.42691506945</v>
+      </c>
+      <c r="B203" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46018.43385951389</v>
+      </c>
+      <c r="B204" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46018.44080395834</v>
+      </c>
+      <c r="B205" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46018.44774840278</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46018.45469284722</v>
+      </c>
+      <c r="B207" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46018.46163729166</v>
+      </c>
+      <c r="B208" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46018.46858173611</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46018.47552618055</v>
+      </c>
+      <c r="B210" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46018.482470625</v>
+      </c>
+      <c r="B211" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46018.48941506945</v>
+      </c>
+      <c r="B212" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46018.49635951389</v>
+      </c>
+      <c r="B213" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46018.50330395834</v>
+      </c>
+      <c r="B214" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46018.51024840278</v>
+      </c>
+      <c r="B215" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46018.51719284722</v>
+      </c>
+      <c r="B216" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46018.52413729166</v>
+      </c>
+      <c r="B217" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46018.53108173611</v>
+      </c>
+      <c r="B218" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46018.53802618055</v>
+      </c>
+      <c r="B219" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46018.544970625</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46018.55191506945</v>
+      </c>
+      <c r="B221" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46018.55885951389</v>
+      </c>
+      <c r="B222" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46018.56580395834</v>
+      </c>
+      <c r="B223" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46018.57274840278</v>
+      </c>
+      <c r="B224" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46018.57969284722</v>
+      </c>
+      <c r="B225" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46018.58663729166</v>
+      </c>
+      <c r="B226" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46018.59358173611</v>
+      </c>
+      <c r="B227" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46018.60052618055</v>
+      </c>
+      <c r="B228" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46018.607470625</v>
+      </c>
+      <c r="B229" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46018.61441506945</v>
+      </c>
+      <c r="B230" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46018.62135951389</v>
+      </c>
+      <c r="B231" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46018.62830395834</v>
+      </c>
+      <c r="B232" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46018.63524840278</v>
+      </c>
+      <c r="B233" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46018.64219284722</v>
+      </c>
+      <c r="B234" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46018.64913729166</v>
+      </c>
+      <c r="B235" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46018.65608173611</v>
+      </c>
+      <c r="B236" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46018.66302618055</v>
+      </c>
+      <c r="B237" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46018.669970625</v>
+      </c>
+      <c r="B238" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46018.67691506945</v>
+      </c>
+      <c r="B239" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46018.68385951389</v>
+      </c>
+      <c r="B240" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46018.69080395834</v>
+      </c>
+      <c r="B241" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46018.69774840278</v>
+      </c>
+      <c r="B242" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46018.70469284722</v>
+      </c>
+      <c r="B243" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46018.71163729166</v>
+      </c>
+      <c r="B244" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46018.71858173611</v>
+      </c>
+      <c r="B245" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46018.72552618055</v>
+      </c>
+      <c r="B246" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46018.732470625</v>
+      </c>
+      <c r="B247" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46018.73941506945</v>
+      </c>
+      <c r="B248" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46018.74635951389</v>
+      </c>
+      <c r="B249" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46018.75330395834</v>
+      </c>
+      <c r="B250" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46018.76024840278</v>
+      </c>
+      <c r="B251" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46018.76719284722</v>
+      </c>
+      <c r="B252" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46018.77413729166</v>
+      </c>
+      <c r="B253" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46018.78108173611</v>
+      </c>
+      <c r="B254" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46018.78802618055</v>
+      </c>
+      <c r="B255" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46018.794970625</v>
+      </c>
+      <c r="B256" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46018.80191506945</v>
+      </c>
+      <c r="B257" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46018.80885951389</v>
+      </c>
+      <c r="B258" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46018.81580395834</v>
+      </c>
+      <c r="B259" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46018.82274840278</v>
+      </c>
+      <c r="B260" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46018.82969284722</v>
+      </c>
+      <c r="B261" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46018.83663729166</v>
+      </c>
+      <c r="B262" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46018.84358173611</v>
+      </c>
+      <c r="B263" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46018.85052618055</v>
+      </c>
+      <c r="B264" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46018.857470625</v>
+      </c>
+      <c r="B265" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46018.86441506945</v>
+      </c>
+      <c r="B266" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46018.87135951389</v>
+      </c>
+      <c r="B267" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46018.87830395834</v>
+      </c>
+      <c r="B268" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46018.88524840278</v>
+      </c>
+      <c r="B269" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46018.89219284722</v>
+      </c>
+      <c r="B270" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46018.89913729166</v>
+      </c>
+      <c r="B271" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46018.90608173611</v>
+      </c>
+      <c r="B272" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46018.91302618055</v>
+      </c>
+      <c r="B273" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46018.919970625</v>
+      </c>
+      <c r="B274" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46018.92691506945</v>
+      </c>
+      <c r="B275" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46018.93385951389</v>
+      </c>
+      <c r="B276" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46018.94080395834</v>
+      </c>
+      <c r="B277" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46018.94774840278</v>
+      </c>
+      <c r="B278" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46018.95469284722</v>
+      </c>
+      <c r="B279" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46018.96163729166</v>
+      </c>
+      <c r="B280" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46018.96858173611</v>
+      </c>
+      <c r="B281" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46018.97552618055</v>
+      </c>
+      <c r="B282" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46018.982470625</v>
+      </c>
+      <c r="B283" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46018.98941506945</v>
+      </c>
+      <c r="B284" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>46018.99635951389</v>
+      </c>
+      <c r="B285" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>46019.00330395834</v>
+      </c>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>46019.01024840278</v>
+      </c>
+      <c r="B287" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>46019.01719284722</v>
+      </c>
+      <c r="B288" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>46019.02413729166</v>
+      </c>
+      <c r="B289" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>46019.03108173611</v>
+      </c>
+      <c r="B290" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>46019.03802618055</v>
+      </c>
+      <c r="B291" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>46019.044970625</v>
+      </c>
+      <c r="B292" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>46019.05191506945</v>
+      </c>
+      <c r="B293" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>46019.05885951389</v>
+      </c>
+      <c r="B294" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>46019.06580395834</v>
+      </c>
+      <c r="B295" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>46019.07274840278</v>
+      </c>
+      <c r="B296" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>46019.07969284722</v>
+      </c>
+      <c r="B297" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>46019.08663729166</v>
+      </c>
+      <c r="B298" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>46019.09358173611</v>
+      </c>
+      <c r="B299" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>46019.10052618055</v>
+      </c>
+      <c r="B300" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>46019.107470625</v>
+      </c>
+      <c r="B301" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>46019.11441506945</v>
+      </c>
+      <c r="B302" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>46019.12135951389</v>
+      </c>
+      <c r="B303" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>46019.12830395834</v>
+      </c>
+      <c r="B304" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>46019.13524840278</v>
+      </c>
+      <c r="B305" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>46019.14219284722</v>
+      </c>
+      <c r="B306" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>46019.14913729166</v>
+      </c>
+      <c r="B307" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>46019.15608173611</v>
+      </c>
+      <c r="B308" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>46019.16302618055</v>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>46019.169970625</v>
+      </c>
+      <c r="B310" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>46019.17691506945</v>
+      </c>
+      <c r="B311" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>46019.18385951389</v>
+      </c>
+      <c r="B312" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>46019.19080395834</v>
+      </c>
+      <c r="B313" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>46019.19774840278</v>
+      </c>
+      <c r="B314" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>46019.20469284722</v>
+      </c>
+      <c r="B315" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>46019.21163729166</v>
+      </c>
+      <c r="B316" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>46019.21858173611</v>
+      </c>
+      <c r="B317" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>46019.22552618055</v>
+      </c>
+      <c r="B318" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>46019.232470625</v>
+      </c>
+      <c r="B319" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>46019.23941506945</v>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>46019.24635951389</v>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>46019.25330395834</v>
+      </c>
+      <c r="B322" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>46019.26024840278</v>
+      </c>
+      <c r="B323" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>46019.26719284722</v>
+      </c>
+      <c r="B324" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>46019.27413729166</v>
+      </c>
+      <c r="B325" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>46019.28108173611</v>
+      </c>
+      <c r="B326" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>46019.28802618055</v>
+      </c>
+      <c r="B327" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>46019.294970625</v>
+      </c>
+      <c r="B328" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>46019.30191506945</v>
+      </c>
+      <c r="B329" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>46019.30885951389</v>
+      </c>
+      <c r="B330" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>46019.31580395834</v>
+      </c>
+      <c r="B331" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>46019.32274840278</v>
+      </c>
+      <c r="B332" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>46019.32969284722</v>
+      </c>
+      <c r="B333" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>46019.33663729166</v>
+      </c>
+      <c r="B334" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>46019.34358173611</v>
+      </c>
+      <c r="B335" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>46019.35052618055</v>
+      </c>
+      <c r="B336" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>46019.357470625</v>
+      </c>
+      <c r="B337" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>46019.36441506945</v>
+      </c>
+      <c r="B338" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>46019.37135951389</v>
+      </c>
+      <c r="B339" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>46019.37830395834</v>
+      </c>
+      <c r="B340" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n">
+        <v>46019.38524840278</v>
+      </c>
+      <c r="B341" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>46019.39219284722</v>
+      </c>
+      <c r="B342" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n">
+        <v>46019.39913729166</v>
+      </c>
+      <c r="B343" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>46019.40608173611</v>
+      </c>
+      <c r="B344" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>46019.41302618055</v>
+      </c>
+      <c r="B345" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>46019.419970625</v>
+      </c>
+      <c r="B346" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>46019.42691506945</v>
+      </c>
+      <c r="B347" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>46019.43385951389</v>
+      </c>
+      <c r="B348" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>46019.44080395834</v>
+      </c>
+      <c r="B349" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>46019.44774840278</v>
+      </c>
+      <c r="B350" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>46019.45469284722</v>
+      </c>
+      <c r="B351" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>46019.46163729166</v>
+      </c>
+      <c r="B352" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>46019.46858173611</v>
+      </c>
+      <c r="B353" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>46019.47552618055</v>
+      </c>
+      <c r="B354" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>46019.482470625</v>
+      </c>
+      <c r="B355" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n">
+        <v>46019.48941506945</v>
+      </c>
+      <c r="B356" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n">
+        <v>46019.49635951389</v>
+      </c>
+      <c r="B357" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n">
+        <v>46019.50330395834</v>
+      </c>
+      <c r="B358" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n">
+        <v>46019.51024840278</v>
+      </c>
+      <c r="B359" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>46019.51719284722</v>
+      </c>
+      <c r="B360" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>46019.52413729166</v>
+      </c>
+      <c r="B361" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>46019.53108173611</v>
+      </c>
+      <c r="B362" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>46019.53802618055</v>
+      </c>
+      <c r="B363" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>46019.544970625</v>
+      </c>
+      <c r="B364" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>46019.55191506945</v>
+      </c>
+      <c r="B365" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>46019.55885951389</v>
+      </c>
+      <c r="B366" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>46019.56580395834</v>
+      </c>
+      <c r="B367" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>46019.57274840278</v>
+      </c>
+      <c r="B368" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>46019.57969284722</v>
+      </c>
+      <c r="B369" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>46019.58663729166</v>
+      </c>
+      <c r="B370" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>46019.59358173611</v>
+      </c>
+      <c r="B371" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>46019.60052618055</v>
+      </c>
+      <c r="B372" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>46019.607470625</v>
+      </c>
+      <c r="B373" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>46019.61441506945</v>
+      </c>
+      <c r="B374" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>46019.62135951389</v>
+      </c>
+      <c r="B375" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>46019.62830395834</v>
+      </c>
+      <c r="B376" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>46019.63524840278</v>
+      </c>
+      <c r="B377" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>46019.64219284722</v>
+      </c>
+      <c r="B378" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>46019.64913729166</v>
+      </c>
+      <c r="B379" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>46019.65608173611</v>
+      </c>
+      <c r="B380" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>46019.66302618055</v>
+      </c>
+      <c r="B381" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>46019.669970625</v>
+      </c>
+      <c r="B382" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>46019.67691506945</v>
+      </c>
+      <c r="B383" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>46019.68385951389</v>
+      </c>
+      <c r="B384" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>46019.69080395834</v>
+      </c>
+      <c r="B385" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>46019.69774840278</v>
+      </c>
+      <c r="B386" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>46019.70469284722</v>
+      </c>
+      <c r="B387" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>46019.71163729166</v>
+      </c>
+      <c r="B388" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>46019.71858173611</v>
+      </c>
+      <c r="B389" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>46019.72552618055</v>
+      </c>
+      <c r="B390" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>46019.732470625</v>
+      </c>
+      <c r="B391" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>46019.73941506945</v>
+      </c>
+      <c r="B392" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>46019.74635951389</v>
+      </c>
+      <c r="B393" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>46019.75330395834</v>
+      </c>
+      <c r="B394" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>46019.76024840278</v>
+      </c>
+      <c r="B395" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>46019.76719284722</v>
+      </c>
+      <c r="B396" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>46019.77413729166</v>
+      </c>
+      <c r="B397" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>46019.78108173611</v>
+      </c>
+      <c r="B398" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>46019.78710940972</v>
+      </c>
+      <c r="B399" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>46019.78725230324</v>
+      </c>
+      <c r="B400" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>46019.78739605324</v>
+      </c>
+      <c r="B401" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>46019.78754708333</v>
+      </c>
+      <c r="B402" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>46019.78770908565</v>
+      </c>
+      <c r="B403" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>46019.7878722801</v>
+      </c>
+      <c r="B404" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>46019.78802618055</v>
+      </c>
+      <c r="B405" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>46019.78803903935</v>
+      </c>
+      <c r="B406" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>46019.78819797454</v>
+      </c>
+      <c r="B407" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>46019.78837785879</v>
+      </c>
+      <c r="B408" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>46019.78855489584</v>
+      </c>
+      <c r="B409" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>46019.788728125</v>
+      </c>
+      <c r="B410" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>46019.78890439815</v>
+      </c>
+      <c r="B411" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>46019.78909473379</v>
+      </c>
+      <c r="B412" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>46019.78927900463</v>
+      </c>
+      <c r="B413" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>46019.78945652777</v>
+      </c>
+      <c r="B414" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>46019.78962299768</v>
+      </c>
+      <c r="B415" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>46019.794970625</v>
+      </c>
+      <c r="B416" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>46019.79917954861</v>
+      </c>
+      <c r="B417" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>46019.79933003472</v>
+      </c>
+      <c r="B418" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>46019.79948458333</v>
+      </c>
+      <c r="B419" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>46019.79964241898</v>
+      </c>
+      <c r="B420" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>46019.79980773148</v>
+      </c>
+      <c r="B421" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>46019.79997678241</v>
+      </c>
+      <c r="B422" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>46019.80014923611</v>
+      </c>
+      <c r="B423" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>46019.80032202546</v>
+      </c>
+      <c r="B424" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>46019.80050456018</v>
+      </c>
+      <c r="B425" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>46019.80069651621</v>
+      </c>
+      <c r="B426" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>46019.80088616898</v>
+      </c>
+      <c r="B427" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>46019.80106292824</v>
+      </c>
+      <c r="B428" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>46019.80124872685</v>
+      </c>
+      <c r="B429" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>46019.80143684028</v>
+      </c>
+      <c r="B430" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>46019.80161681713</v>
+      </c>
+      <c r="B431" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>46019.8017946412</v>
+      </c>
+      <c r="B432" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>46019.80191506945</v>
+      </c>
+      <c r="B433" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>46019.80630458333</v>
+      </c>
+      <c r="B434" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>46019.80639174768</v>
+      </c>
+      <c r="B435" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>46019.80648799769</v>
+      </c>
+      <c r="B436" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>46019.80657899306</v>
+      </c>
+      <c r="B437" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>46019.80667068287</v>
+      </c>
+      <c r="B438" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>46019.8067622338</v>
+      </c>
+      <c r="B439" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>46019.80685096065</v>
+      </c>
+      <c r="B440" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>46019.80694037037</v>
+      </c>
+      <c r="B441" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>46019.80702836806</v>
+      </c>
+      <c r="B442" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>46019.80712328704</v>
+      </c>
+      <c r="B443" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>46019.80722640047</v>
+      </c>
+      <c r="B444" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>46019.80732671297</v>
+      </c>
+      <c r="B445" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>46019.80742377315</v>
+      </c>
+      <c r="B446" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>46019.8671515625</v>
+      </c>
+      <c r="B447" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>46019.86730526621</v>
+      </c>
+      <c r="B448" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>46019.86745759259</v>
+      </c>
+      <c r="B449" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>46019.86760027778</v>
+      </c>
+      <c r="B450" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>46019.86774581019</v>
+      </c>
+      <c r="B451" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>46019.86789157407</v>
+      </c>
+      <c r="B452" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>46019.86804280092</v>
+      </c>
+      <c r="B453" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>46019.86819030093</v>
+      </c>
+      <c r="B454" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>46019.86834508102</v>
+      </c>
+      <c r="B455" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>46019.86854447917</v>
+      </c>
+      <c r="B456" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>46019.86981938657</v>
+      </c>
+      <c r="B457" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
         <v>46019.87001287037</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B458" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>46019.87890775463</v>
+      </c>
+      <c r="B459" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>46019.87906486111</v>
+      </c>
+      <c r="B460" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>46019.87922371528</v>
+      </c>
+      <c r="B461" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>46019.87936680556</v>
+      </c>
+      <c r="B462" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>46019.87950716435</v>
+      </c>
+      <c r="B463" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>46019.87965185185</v>
+      </c>
+      <c r="B464" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>46019.87980674768</v>
+      </c>
+      <c r="B465" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>46019.87996484954</v>
+      </c>
+      <c r="B466" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>46019.88012774305</v>
+      </c>
+      <c r="B467" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>46019.90720983796</v>
+      </c>
+      <c r="B468" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>46019.90729984954</v>
+      </c>
+      <c r="B469" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>46019.90739475694</v>
+      </c>
+      <c r="B470" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>46019.9074912037</v>
+      </c>
+      <c r="B471" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
+        <v>46019.90758472222</v>
+      </c>
+      <c r="B472" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>46019.90768146991</v>
+      </c>
+      <c r="B473" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>46019.90777574074</v>
+      </c>
+      <c r="B474" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>46019.90787814815</v>
+      </c>
+      <c r="B475" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>46019.90797552084</v>
+      </c>
+      <c r="B476" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>46019.90807</v>
+      </c>
+      <c r="B477" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>46019.90816299769</v>
+      </c>
+      <c r="B478" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>46019.90827078704</v>
+      </c>
+      <c r="B479" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>46019.9083687963</v>
+      </c>
+      <c r="B480" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n">
+        <v>46019.90847293982</v>
+      </c>
+      <c r="B481" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="n">
+        <v>46019.9085774074</v>
+      </c>
+      <c r="B482" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n">
+        <v>46019.90868396991</v>
+      </c>
+      <c r="B483" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n">
+        <v>46019.90879077547</v>
+      </c>
+      <c r="B484" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n">
+        <v>46019.90888137731</v>
+      </c>
+      <c r="B485" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>46020.39276376157</v>
+      </c>
+      <c r="B486" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>46020.39292097222</v>
+      </c>
+      <c r="B487" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>46020.39307635416</v>
+      </c>
+      <c r="B488" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>46020.39323398148</v>
+      </c>
+      <c r="B489" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>46020.39341068287</v>
+      </c>
+      <c r="B490" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>46020.39359583333</v>
+      </c>
+      <c r="B491" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>46020.39377560185</v>
+      </c>
+      <c r="B492" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>46020.39395383102</v>
+      </c>
+      <c r="B493" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>46020.39413903935</v>
+      </c>
+      <c r="B494" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>46020.39432732639</v>
+      </c>
+      <c r="B495" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>46020.39451603009</v>
+      </c>
+      <c r="B496" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>46020.39471405093</v>
+      </c>
+      <c r="B497" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>46020.39490146991</v>
+      </c>
+      <c r="B498" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>46020.39510195602</v>
+      </c>
+      <c r="B499" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n">
+        <v>46020.39528770834</v>
+      </c>
+      <c r="B500" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>46020.39546400463</v>
+      </c>
+      <c r="B501" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/temp.xlsx
+++ b/temp.xlsx
@@ -446,215 +446,215 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46017.03108173611</v>
+        <v>46019.482470625</v>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46017.03802618055</v>
+        <v>46019.48941506945</v>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46017.044970625</v>
+        <v>46019.49635951389</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46017.05191506945</v>
+        <v>46019.50330395834</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46017.05885951389</v>
+        <v>46019.51024840278</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46017.06580395834</v>
+        <v>46019.51719284722</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46017.07274840278</v>
+        <v>46019.52413729166</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46017.07969284722</v>
+        <v>46019.53108173611</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46017.08663729166</v>
+        <v>46019.53802618055</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46017.09358173611</v>
+        <v>46019.544970625</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46017.10052618055</v>
+        <v>46019.55191506945</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46017.107470625</v>
+        <v>46019.55885951389</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46017.11441506945</v>
+        <v>46019.56580395834</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46017.12135951389</v>
+        <v>46019.57274840278</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46017.12830395834</v>
+        <v>46019.57969284722</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46017.13524840278</v>
+        <v>46019.58663729166</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46017.14219284722</v>
+        <v>46019.59358173611</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46017.14913729166</v>
+        <v>46019.60052618055</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46017.15608173611</v>
+        <v>46019.607470625</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46017.16302618055</v>
+        <v>46019.61441506945</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46017.169970625</v>
+        <v>46019.62135951389</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46017.17691506945</v>
+        <v>46019.62830395834</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46017.18385951389</v>
+        <v>46019.63524840278</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46017.19080395834</v>
+        <v>46019.64219284722</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46017.19774840278</v>
+        <v>46019.64913729166</v>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46017.20469284722</v>
+        <v>46019.65608173611</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46017.21163729166</v>
+        <v>46019.66302618055</v>
       </c>
       <c r="B28" t="n">
         <v>9</v>
@@ -662,359 +662,359 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46017.21858173611</v>
+        <v>46019.669970625</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46017.22552618055</v>
+        <v>46019.67691506945</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46017.232470625</v>
+        <v>46019.68385951389</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46017.23941506945</v>
+        <v>46019.69080395834</v>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46017.24635951389</v>
+        <v>46019.69774840278</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46017.25330395834</v>
+        <v>46019.70469284722</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46017.26024840278</v>
+        <v>46019.71163729166</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46017.26719284722</v>
+        <v>46019.71858173611</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46017.27413729166</v>
+        <v>46019.72552618055</v>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46017.28108173611</v>
+        <v>46019.732470625</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46017.28802618055</v>
+        <v>46019.73941506945</v>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46017.294970625</v>
+        <v>46019.74635951389</v>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46017.30191506945</v>
+        <v>46019.75330395834</v>
       </c>
       <c r="B41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46017.30885951389</v>
+        <v>46019.76024840278</v>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46017.31580395834</v>
+        <v>46019.76719284722</v>
       </c>
       <c r="B43" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46017.32274840278</v>
+        <v>46019.77413729166</v>
       </c>
       <c r="B44" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46017.32969284722</v>
+        <v>46019.78108173611</v>
       </c>
       <c r="B45" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46017.33663729166</v>
+        <v>46019.78710940972</v>
       </c>
       <c r="B46" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46017.34358173611</v>
+        <v>46019.78725230324</v>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46017.35052618055</v>
+        <v>46019.78739605324</v>
       </c>
       <c r="B48" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46017.357470625</v>
+        <v>46019.78754708333</v>
       </c>
       <c r="B49" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46017.36441506945</v>
+        <v>46019.78770908565</v>
       </c>
       <c r="B50" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46017.37135951389</v>
+        <v>46019.7878722801</v>
       </c>
       <c r="B51" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46017.37830395834</v>
+        <v>46019.78802618055</v>
       </c>
       <c r="B52" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46017.38524840278</v>
+        <v>46019.78803903935</v>
       </c>
       <c r="B53" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46017.39219284722</v>
+        <v>46019.78819797454</v>
       </c>
       <c r="B54" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46017.39913729166</v>
+        <v>46019.78837785879</v>
       </c>
       <c r="B55" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46017.40608173611</v>
+        <v>46019.78855489584</v>
       </c>
       <c r="B56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46017.41302618055</v>
+        <v>46019.788728125</v>
       </c>
       <c r="B57" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46017.419970625</v>
+        <v>46019.78890439815</v>
       </c>
       <c r="B58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46017.42691506945</v>
+        <v>46019.78909473379</v>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46017.43385951389</v>
+        <v>46019.78927900463</v>
       </c>
       <c r="B60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46017.44080395834</v>
+        <v>46019.78945652777</v>
       </c>
       <c r="B61" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46017.44774840278</v>
+        <v>46019.78962299768</v>
       </c>
       <c r="B62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46017.45469284722</v>
+        <v>46019.794970625</v>
       </c>
       <c r="B63" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46017.46163729166</v>
+        <v>46019.79917954861</v>
       </c>
       <c r="B64" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46017.46858173611</v>
+        <v>46019.79933003472</v>
       </c>
       <c r="B65" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46017.47552618055</v>
+        <v>46019.79948458333</v>
       </c>
       <c r="B66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46017.482470625</v>
+        <v>46019.79964241898</v>
       </c>
       <c r="B67" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46017.48941506945</v>
+        <v>46019.79980773148</v>
       </c>
       <c r="B68" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46017.49635951389</v>
+        <v>46019.79997678241</v>
       </c>
       <c r="B69" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46017.50330395834</v>
+        <v>46019.80014923611</v>
       </c>
       <c r="B70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46017.51024840278</v>
+        <v>46019.80032202546</v>
       </c>
       <c r="B71" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46017.51719284722</v>
+        <v>46019.80050456018</v>
       </c>
       <c r="B72" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46017.52413729166</v>
+        <v>46019.80069651621</v>
       </c>
       <c r="B73" t="n">
         <v>9</v>
@@ -1022,39 +1022,39 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46017.53108173611</v>
+        <v>46019.80088616898</v>
       </c>
       <c r="B74" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46017.53802618055</v>
+        <v>46019.80106292824</v>
       </c>
       <c r="B75" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46017.544970625</v>
+        <v>46019.80124872685</v>
       </c>
       <c r="B76" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46017.55191506945</v>
+        <v>46019.80143684028</v>
       </c>
       <c r="B77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46017.55885951389</v>
+        <v>46019.80161681713</v>
       </c>
       <c r="B78" t="n">
         <v>9</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46017.56580395834</v>
+        <v>46019.8017946412</v>
       </c>
       <c r="B79" t="n">
         <v>12</v>
@@ -1070,447 +1070,447 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46017.57274840278</v>
+        <v>46019.80191506945</v>
       </c>
       <c r="B80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46017.57969284722</v>
+        <v>46019.80630458333</v>
       </c>
       <c r="B81" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46017.58663729166</v>
+        <v>46019.80639174768</v>
       </c>
       <c r="B82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46017.59358173611</v>
+        <v>46019.80648799769</v>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46017.60052618055</v>
+        <v>46019.80657899306</v>
       </c>
       <c r="B84" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46017.607470625</v>
+        <v>46019.80667068287</v>
       </c>
       <c r="B85" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46017.61441506945</v>
+        <v>46019.8067622338</v>
       </c>
       <c r="B86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46017.62135951389</v>
+        <v>46019.80685096065</v>
       </c>
       <c r="B87" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46017.62830395834</v>
+        <v>46019.80694037037</v>
       </c>
       <c r="B88" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46017.63524840278</v>
+        <v>46019.80702836806</v>
       </c>
       <c r="B89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46017.64219284722</v>
+        <v>46019.80712328704</v>
       </c>
       <c r="B90" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46017.64913729166</v>
+        <v>46019.80722640047</v>
       </c>
       <c r="B91" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46017.65608173611</v>
+        <v>46019.80732671297</v>
       </c>
       <c r="B92" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46017.66302618055</v>
+        <v>46019.80742377315</v>
       </c>
       <c r="B93" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46017.669970625</v>
+        <v>46019.8671515625</v>
       </c>
       <c r="B94" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46017.67691506945</v>
+        <v>46019.86730526621</v>
       </c>
       <c r="B95" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46017.68385951389</v>
+        <v>46019.86745759259</v>
       </c>
       <c r="B96" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46017.69080395834</v>
+        <v>46019.86760027778</v>
       </c>
       <c r="B97" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46017.69774840278</v>
+        <v>46019.86774581019</v>
       </c>
       <c r="B98" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46017.70469284722</v>
+        <v>46019.86789157407</v>
       </c>
       <c r="B99" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46017.71163729166</v>
+        <v>46019.86804280092</v>
       </c>
       <c r="B100" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46017.71858173611</v>
+        <v>46019.86819030093</v>
       </c>
       <c r="B101" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46017.72552618055</v>
+        <v>46019.86834508102</v>
       </c>
       <c r="B102" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46017.732470625</v>
+        <v>46019.86854447917</v>
       </c>
       <c r="B103" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46017.73941506945</v>
+        <v>46019.86981938657</v>
       </c>
       <c r="B104" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46017.74635951389</v>
+        <v>46019.87001287037</v>
       </c>
       <c r="B105" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46017.75330395834</v>
+        <v>46019.87890775463</v>
       </c>
       <c r="B106" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46017.76024840278</v>
+        <v>46019.87906486111</v>
       </c>
       <c r="B107" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46017.76719284722</v>
+        <v>46019.87922371528</v>
       </c>
       <c r="B108" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46017.77413729166</v>
+        <v>46019.87936680556</v>
       </c>
       <c r="B109" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46017.78108173611</v>
+        <v>46019.87950716435</v>
       </c>
       <c r="B110" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46017.78802618055</v>
+        <v>46019.87965185185</v>
       </c>
       <c r="B111" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46017.794970625</v>
+        <v>46019.87980674768</v>
       </c>
       <c r="B112" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46017.80191506945</v>
+        <v>46019.87996484954</v>
       </c>
       <c r="B113" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46017.80885951389</v>
+        <v>46019.88012774305</v>
       </c>
       <c r="B114" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46017.81580395834</v>
+        <v>46019.90720983796</v>
       </c>
       <c r="B115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46017.82274840278</v>
+        <v>46019.90729984954</v>
       </c>
       <c r="B116" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46017.82969284722</v>
+        <v>46019.90739475694</v>
       </c>
       <c r="B117" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46017.83663729166</v>
+        <v>46019.9074912037</v>
       </c>
       <c r="B118" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46017.84358173611</v>
+        <v>46019.90758472222</v>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46017.85052618055</v>
+        <v>46019.90768146991</v>
       </c>
       <c r="B120" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46017.857470625</v>
+        <v>46019.90777574074</v>
       </c>
       <c r="B121" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46017.86441506945</v>
+        <v>46019.90787814815</v>
       </c>
       <c r="B122" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46017.87135951389</v>
+        <v>46019.90797552084</v>
       </c>
       <c r="B123" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46017.87830395834</v>
+        <v>46019.90807</v>
       </c>
       <c r="B124" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46017.88524840278</v>
+        <v>46019.90816299769</v>
       </c>
       <c r="B125" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46017.89219284722</v>
+        <v>46019.90827078704</v>
       </c>
       <c r="B126" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46017.89913729166</v>
+        <v>46019.9083687963</v>
       </c>
       <c r="B127" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46017.90608173611</v>
+        <v>46019.90847293982</v>
       </c>
       <c r="B128" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46017.91302618055</v>
+        <v>46019.9085774074</v>
       </c>
       <c r="B129" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46017.919970625</v>
+        <v>46019.90868396991</v>
       </c>
       <c r="B130" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017.92691506945</v>
+        <v>46019.90879077547</v>
       </c>
       <c r="B131" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46017.93385951389</v>
+        <v>46019.90888137731</v>
       </c>
       <c r="B132" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46017.94080395834</v>
+        <v>46020.39276376157</v>
       </c>
       <c r="B133" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46017.94774840278</v>
+        <v>46020.39292097222</v>
       </c>
       <c r="B134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46017.95469284722</v>
+        <v>46020.39307635416</v>
       </c>
       <c r="B135" t="n">
         <v>5</v>
@@ -1518,47 +1518,47 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46017.96163729166</v>
+        <v>46020.39323398148</v>
       </c>
       <c r="B136" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46017.96858173611</v>
+        <v>46020.39341068287</v>
       </c>
       <c r="B137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46017.97552618055</v>
+        <v>46020.39359583333</v>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46017.982470625</v>
+        <v>46020.39377560185</v>
       </c>
       <c r="B139" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46017.98941506945</v>
+        <v>46020.39395383102</v>
       </c>
       <c r="B140" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46017.99635951389</v>
+        <v>46020.39413903935</v>
       </c>
       <c r="B141" t="n">
         <v>13</v>
@@ -1566,95 +1566,95 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46018.00330395834</v>
+        <v>46020.39432732639</v>
       </c>
       <c r="B142" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46018.01024840278</v>
+        <v>46020.39451603009</v>
       </c>
       <c r="B143" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46018.01719284722</v>
+        <v>46020.39471405093</v>
       </c>
       <c r="B144" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46018.02413729166</v>
+        <v>46020.39490146991</v>
       </c>
       <c r="B145" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46018.03108173611</v>
+        <v>46020.39510195602</v>
       </c>
       <c r="B146" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46018.03802618055</v>
+        <v>46020.39528770834</v>
       </c>
       <c r="B147" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46018.044970625</v>
+        <v>46020.39546400463</v>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46018.05191506945</v>
+        <v>46026.66744793981</v>
       </c>
       <c r="B149" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46018.05885951389</v>
+        <v>46026.66754082176</v>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46018.06580395834</v>
+        <v>46026.66764</v>
       </c>
       <c r="B151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46018.07274840278</v>
+        <v>46026.66773288194</v>
       </c>
       <c r="B152" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46018.07969284722</v>
+        <v>46026.84504885416</v>
       </c>
       <c r="B153" t="n">
         <v>6</v>
@@ -1662,71 +1662,71 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46018.08663729166</v>
+        <v>46026.84519724537</v>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46018.09358173611</v>
+        <v>46026.84534662037</v>
       </c>
       <c r="B155" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46018.10052618055</v>
+        <v>46026.84549210648</v>
       </c>
       <c r="B156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46018.107470625</v>
+        <v>46026.84564409722</v>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46018.11441506945</v>
+        <v>46026.84579767361</v>
       </c>
       <c r="B158" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46018.12135951389</v>
+        <v>46026.84595106482</v>
       </c>
       <c r="B159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46018.12830395834</v>
+        <v>46026.84610516204</v>
       </c>
       <c r="B160" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46018.13524840278</v>
+        <v>46026.8462952199</v>
       </c>
       <c r="B161" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46018.14219284722</v>
+        <v>46026.84648365741</v>
       </c>
       <c r="B162" t="n">
         <v>9</v>
@@ -1734,95 +1734,95 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46018.14913729166</v>
+        <v>46026.84665377315</v>
       </c>
       <c r="B163" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46018.15608173611</v>
+        <v>46026.84682952546</v>
       </c>
       <c r="B164" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46018.16302618055</v>
+        <v>46026.84701668981</v>
       </c>
       <c r="B165" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46018.169970625</v>
+        <v>46026.8472141088</v>
       </c>
       <c r="B166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46018.17691506945</v>
+        <v>46026.84739814815</v>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46018.18385951389</v>
+        <v>46026.84758951389</v>
       </c>
       <c r="B168" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46018.19080395834</v>
+        <v>46026.85146954861</v>
       </c>
       <c r="B169" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46018.19774840278</v>
+        <v>46026.85162868055</v>
       </c>
       <c r="B170" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46018.20469284722</v>
+        <v>46026.85178583334</v>
       </c>
       <c r="B171" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46018.21163729166</v>
+        <v>46026.85192746528</v>
       </c>
       <c r="B172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46018.21858173611</v>
+        <v>46026.85207039352</v>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46018.22552618055</v>
+        <v>46026.85221849537</v>
       </c>
       <c r="B174" t="n">
         <v>5</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46018.232470625</v>
+        <v>46026.8523769213</v>
       </c>
       <c r="B175" t="n">
         <v>6</v>
@@ -1838,15 +1838,15 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46018.23941506945</v>
+        <v>46026.85252752315</v>
       </c>
       <c r="B176" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46018.24635951389</v>
+        <v>46026.85268261574</v>
       </c>
       <c r="B177" t="n">
         <v>5</v>
@@ -1854,23 +1854,23 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46018.25330395834</v>
+        <v>46026.85283653935</v>
       </c>
       <c r="B178" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46018.26024840278</v>
+        <v>46026.85300480324</v>
       </c>
       <c r="B179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46018.26719284722</v>
+        <v>46026.85316439815</v>
       </c>
       <c r="B180" t="n">
         <v>6</v>
@@ -1878,1119 +1878,1119 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46018.27413729166</v>
+        <v>46026.8533294213</v>
       </c>
       <c r="B181" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46018.28108173611</v>
+        <v>46026.85349019676</v>
       </c>
       <c r="B182" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46018.28802618055</v>
+        <v>46026.8624885301</v>
       </c>
       <c r="B183" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46018.294970625</v>
+        <v>46026.86269910879</v>
       </c>
       <c r="B184" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46018.30191506945</v>
+        <v>46026.86291793981</v>
       </c>
       <c r="B185" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46018.30885951389</v>
+        <v>46026.86314090278</v>
       </c>
       <c r="B186" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46018.31580395834</v>
+        <v>46026.86335069445</v>
       </c>
       <c r="B187" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46018.32274840278</v>
+        <v>46026.86355646991</v>
       </c>
       <c r="B188" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46018.32969284722</v>
+        <v>46026.8637765625</v>
       </c>
       <c r="B189" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46018.33663729166</v>
+        <v>46026.88461734954</v>
       </c>
       <c r="B190" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46018.34358173611</v>
+        <v>46026.88486443287</v>
       </c>
       <c r="B191" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46018.35052618055</v>
+        <v>46026.88511172454</v>
       </c>
       <c r="B192" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46018.357470625</v>
+        <v>46026.88535983796</v>
       </c>
       <c r="B193" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46018.36441506945</v>
+        <v>46026.88560344907</v>
       </c>
       <c r="B194" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46018.37135951389</v>
+        <v>46026.88581584491</v>
       </c>
       <c r="B195" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46018.37830395834</v>
+        <v>46026.88602599537</v>
       </c>
       <c r="B196" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46018.38524840278</v>
+        <v>46026.88623276621</v>
       </c>
       <c r="B197" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46018.39219284722</v>
+        <v>46026.88643908565</v>
       </c>
       <c r="B198" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46018.39913729166</v>
+        <v>46026.88665152778</v>
       </c>
       <c r="B199" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46018.40608173611</v>
+        <v>46026.88686043982</v>
       </c>
       <c r="B200" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46018.41302618055</v>
+        <v>46026.8870656713</v>
       </c>
       <c r="B201" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46018.419970625</v>
+        <v>46026.8876553588</v>
       </c>
       <c r="B202" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46018.42691506945</v>
+        <v>46026.88774811343</v>
       </c>
       <c r="B203" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46018.43385951389</v>
+        <v>46026.88785146991</v>
       </c>
       <c r="B204" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46018.44080395834</v>
+        <v>46026.88794702546</v>
       </c>
       <c r="B205" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46018.44774840278</v>
+        <v>46026.88804637732</v>
       </c>
       <c r="B206" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46018.45469284722</v>
+        <v>46026.88814028935</v>
       </c>
       <c r="B207" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46018.46163729166</v>
+        <v>46026.88823039352</v>
       </c>
       <c r="B208" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46018.46858173611</v>
+        <v>46026.88831609954</v>
       </c>
       <c r="B209" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46018.47552618055</v>
+        <v>46026.88840537037</v>
       </c>
       <c r="B210" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46018.482470625</v>
+        <v>46026.88850217593</v>
       </c>
       <c r="B211" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46018.48941506945</v>
+        <v>46026.88860892361</v>
       </c>
       <c r="B212" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46018.49635951389</v>
+        <v>46026.88870471065</v>
       </c>
       <c r="B213" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46018.50330395834</v>
+        <v>46026.88880355324</v>
       </c>
       <c r="B214" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46018.51024840278</v>
+        <v>46026.88890252315</v>
       </c>
       <c r="B215" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46018.51719284722</v>
+        <v>46026.8889945949</v>
       </c>
       <c r="B216" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46018.52413729166</v>
+        <v>46026.88908722223</v>
       </c>
       <c r="B217" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46018.53108173611</v>
+        <v>46026.89144305555</v>
       </c>
       <c r="B218" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46018.53802618055</v>
+        <v>46026.89153149306</v>
       </c>
       <c r="B219" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46018.544970625</v>
+        <v>46026.89163181713</v>
       </c>
       <c r="B220" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46018.55191506945</v>
+        <v>46026.8917240625</v>
       </c>
       <c r="B221" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46018.55885951389</v>
+        <v>46026.89181844908</v>
       </c>
       <c r="B222" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46018.56580395834</v>
+        <v>46026.89191233796</v>
       </c>
       <c r="B223" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46018.57274840278</v>
+        <v>46026.89200091435</v>
       </c>
       <c r="B224" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46018.57969284722</v>
+        <v>46026.8920865625</v>
       </c>
       <c r="B225" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46018.58663729166</v>
+        <v>46026.89217583333</v>
       </c>
       <c r="B226" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46018.59358173611</v>
+        <v>46026.89227427083</v>
       </c>
       <c r="B227" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46018.60052618055</v>
+        <v>46026.89238376157</v>
       </c>
       <c r="B228" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46018.607470625</v>
+        <v>46026.89247775463</v>
       </c>
       <c r="B229" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46018.61441506945</v>
+        <v>46026.89257701389</v>
       </c>
       <c r="B230" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46018.62135951389</v>
+        <v>46026.89267527778</v>
       </c>
       <c r="B231" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46018.62830395834</v>
+        <v>46026.89276756944</v>
       </c>
       <c r="B232" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46018.63524840278</v>
+        <v>46026.8928577662</v>
       </c>
       <c r="B233" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46018.64219284722</v>
+        <v>46026.92605893518</v>
       </c>
       <c r="B234" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46018.64913729166</v>
+        <v>46026.92615020833</v>
       </c>
       <c r="B235" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46018.65608173611</v>
+        <v>46026.92625466435</v>
       </c>
       <c r="B236" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46018.66302618055</v>
+        <v>46026.92635145834</v>
       </c>
       <c r="B237" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46018.669970625</v>
+        <v>46026.92645037037</v>
       </c>
       <c r="B238" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46018.67691506945</v>
+        <v>46026.9265515625</v>
       </c>
       <c r="B239" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46018.68385951389</v>
+        <v>46026.92664177083</v>
       </c>
       <c r="B240" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46018.69080395834</v>
+        <v>46026.92672975695</v>
       </c>
       <c r="B241" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46018.69774840278</v>
+        <v>46026.92682028935</v>
       </c>
       <c r="B242" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46018.70469284722</v>
+        <v>46026.92691865741</v>
       </c>
       <c r="B243" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46018.71163729166</v>
+        <v>46026.92703364584</v>
       </c>
       <c r="B244" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46018.71858173611</v>
+        <v>46026.927139375</v>
       </c>
       <c r="B245" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46018.72552618055</v>
+        <v>46026.92724979167</v>
       </c>
       <c r="B246" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46018.732470625</v>
+        <v>46026.9273508449</v>
       </c>
       <c r="B247" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46018.73941506945</v>
+        <v>46026.92744684028</v>
       </c>
       <c r="B248" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46018.74635951389</v>
+        <v>46026.92753928241</v>
       </c>
       <c r="B249" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46018.75330395834</v>
+        <v>46026.93439672454</v>
       </c>
       <c r="B250" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46018.76024840278</v>
+        <v>46026.93449265046</v>
       </c>
       <c r="B251" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46018.76719284722</v>
+        <v>46026.93459239583</v>
       </c>
       <c r="B252" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>46018.77413729166</v>
+        <v>46026.93468439815</v>
       </c>
       <c r="B253" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>46018.78108173611</v>
+        <v>46026.93478238426</v>
       </c>
       <c r="B254" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>46018.78802618055</v>
+        <v>46026.93489512731</v>
       </c>
       <c r="B255" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>46018.794970625</v>
+        <v>46026.93498572917</v>
       </c>
       <c r="B256" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>46018.80191506945</v>
+        <v>46026.93506887731</v>
       </c>
       <c r="B257" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>46018.80885951389</v>
+        <v>46026.93515899305</v>
       </c>
       <c r="B258" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>46018.81580395834</v>
+        <v>46026.93525513889</v>
       </c>
       <c r="B259" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>46018.82274840278</v>
+        <v>46026.93536009259</v>
       </c>
       <c r="B260" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>46018.82969284722</v>
+        <v>46026.93545009259</v>
       </c>
       <c r="B261" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>46018.83663729166</v>
+        <v>46026.93554540509</v>
       </c>
       <c r="B262" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>46018.84358173611</v>
+        <v>46026.93565690972</v>
       </c>
       <c r="B263" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>46018.85052618055</v>
+        <v>46026.93576739584</v>
       </c>
       <c r="B264" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>46018.857470625</v>
+        <v>46026.93587543981</v>
       </c>
       <c r="B265" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>46018.86441506945</v>
+        <v>46026.93799715277</v>
       </c>
       <c r="B266" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>46018.87135951389</v>
+        <v>46026.93808550926</v>
       </c>
       <c r="B267" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>46018.87830395834</v>
+        <v>46026.93819131944</v>
       </c>
       <c r="B268" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>46018.88524840278</v>
+        <v>46026.93828179398</v>
       </c>
       <c r="B269" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>46018.89219284722</v>
+        <v>46026.93837284722</v>
       </c>
       <c r="B270" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>46018.89913729166</v>
+        <v>46026.93846381945</v>
       </c>
       <c r="B271" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>46018.90608173611</v>
+        <v>46026.9385528125</v>
       </c>
       <c r="B272" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>46018.91302618055</v>
+        <v>46026.93863473379</v>
       </c>
       <c r="B273" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>46018.919970625</v>
+        <v>46026.93872153935</v>
       </c>
       <c r="B274" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>46018.92691506945</v>
+        <v>46026.9388149537</v>
       </c>
       <c r="B275" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>46018.93385951389</v>
+        <v>46026.93891840278</v>
       </c>
       <c r="B276" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>46018.94080395834</v>
+        <v>46026.93901035879</v>
       </c>
       <c r="B277" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>46018.94774840278</v>
+        <v>46026.93910686343</v>
       </c>
       <c r="B278" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>46018.95469284722</v>
+        <v>46026.93920134259</v>
       </c>
       <c r="B279" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>46018.96163729166</v>
+        <v>46026.93929981482</v>
       </c>
       <c r="B280" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>46018.96858173611</v>
+        <v>46026.93939662037</v>
       </c>
       <c r="B281" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>46018.97552618055</v>
+        <v>46026.94307570602</v>
       </c>
       <c r="B282" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>46018.982470625</v>
+        <v>46026.94316756944</v>
       </c>
       <c r="B283" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>46018.98941506945</v>
+        <v>46026.9432702662</v>
       </c>
       <c r="B284" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>46018.99635951389</v>
+        <v>46026.9433797801</v>
       </c>
       <c r="B285" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>46019.00330395834</v>
+        <v>46026.94347479167</v>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>46019.01024840278</v>
+        <v>46026.94356891204</v>
       </c>
       <c r="B287" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>46019.01719284722</v>
+        <v>46026.94365929398</v>
       </c>
       <c r="B288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>46019.02413729166</v>
+        <v>46026.94374217593</v>
       </c>
       <c r="B289" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>46019.03108173611</v>
+        <v>46026.9438290625</v>
       </c>
       <c r="B290" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>46019.03802618055</v>
+        <v>46026.94393512732</v>
       </c>
       <c r="B291" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>46019.044970625</v>
+        <v>46026.9440396875</v>
       </c>
       <c r="B292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>46019.05191506945</v>
+        <v>46026.94413311343</v>
       </c>
       <c r="B293" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
-        <v>46019.05885951389</v>
+        <v>46026.94422998842</v>
       </c>
       <c r="B294" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
-        <v>46019.06580395834</v>
+        <v>46026.94433020833</v>
       </c>
       <c r="B295" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
-        <v>46019.07274840278</v>
+        <v>46026.94442109954</v>
       </c>
       <c r="B296" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
-        <v>46019.07969284722</v>
+        <v>46026.94451539352</v>
       </c>
       <c r="B297" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
-        <v>46019.08663729166</v>
+        <v>46026.94922541667</v>
       </c>
       <c r="B298" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
-        <v>46019.09358173611</v>
+        <v>46026.94931236111</v>
       </c>
       <c r="B299" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
-        <v>46019.10052618055</v>
+        <v>46026.94941128472</v>
       </c>
       <c r="B300" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
-        <v>46019.107470625</v>
+        <v>46026.94950184028</v>
       </c>
       <c r="B301" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
-        <v>46019.11441506945</v>
+        <v>46026.94959188657</v>
       </c>
       <c r="B302" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
-        <v>46019.12135951389</v>
+        <v>46026.94968196759</v>
       </c>
       <c r="B303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
-        <v>46019.12830395834</v>
+        <v>46026.94976704861</v>
       </c>
       <c r="B304" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
-        <v>46019.13524840278</v>
+        <v>46026.94984835648</v>
       </c>
       <c r="B305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
-        <v>46019.14219284722</v>
+        <v>46026.94993317129</v>
       </c>
       <c r="B306" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
-        <v>46019.14913729166</v>
+        <v>46026.95002974537</v>
       </c>
       <c r="B307" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
-        <v>46019.15608173611</v>
+        <v>46026.95013520833</v>
       </c>
       <c r="B308" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
-        <v>46019.16302618055</v>
+        <v>46026.95022722222</v>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
-        <v>46019.169970625</v>
+        <v>46026.95032533565</v>
       </c>
       <c r="B310" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
-        <v>46019.17691506945</v>
+        <v>46026.95042094908</v>
       </c>
       <c r="B311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
-        <v>46019.18385951389</v>
+        <v>46026.95051561343</v>
       </c>
       <c r="B312" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
-        <v>46019.19080395834</v>
+        <v>46026.95060738426</v>
       </c>
       <c r="B313" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
-        <v>46019.19774840278</v>
+        <v>46026.95872325231</v>
       </c>
       <c r="B314" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
-        <v>46019.20469284722</v>
+        <v>46026.95881356482</v>
       </c>
       <c r="B315" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
-        <v>46019.21163729166</v>
+        <v>46026.958915</v>
       </c>
       <c r="B316" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
-        <v>46019.21858173611</v>
+        <v>46026.95901106481</v>
       </c>
       <c r="B317" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
-        <v>46019.22552618055</v>
+        <v>46026.95911041667</v>
       </c>
       <c r="B318" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
-        <v>46019.232470625</v>
+        <v>46026.95920623843</v>
       </c>
       <c r="B319" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
-        <v>46019.23941506945</v>
+        <v>46026.95929856481</v>
       </c>
       <c r="B320" t="n">
         <v>1</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
-        <v>46019.24635951389</v>
+        <v>46026.95938450231</v>
       </c>
       <c r="B321" t="n">
         <v>1</v>
@@ -3006,1015 +3006,1015 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>46019.25330395834</v>
+        <v>46026.95947372685</v>
       </c>
       <c r="B322" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>46019.26024840278</v>
+        <v>46026.9595902662</v>
       </c>
       <c r="B323" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>46019.26719284722</v>
+        <v>46026.95969628472</v>
       </c>
       <c r="B324" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>46019.27413729166</v>
+        <v>46026.95978834491</v>
       </c>
       <c r="B325" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>46019.28108173611</v>
+        <v>46026.95988446759</v>
       </c>
       <c r="B326" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>46019.28802618055</v>
+        <v>46026.95997978009</v>
       </c>
       <c r="B327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>46019.294970625</v>
+        <v>46026.96007513889</v>
       </c>
       <c r="B328" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>46019.30191506945</v>
+        <v>46026.96016885417</v>
       </c>
       <c r="B329" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>46019.30885951389</v>
+        <v>46026.96187246528</v>
       </c>
       <c r="B330" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>46019.31580395834</v>
+        <v>46026.96196184028</v>
       </c>
       <c r="B331" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>46019.32274840278</v>
+        <v>46026.96206620371</v>
       </c>
       <c r="B332" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>46019.32969284722</v>
+        <v>46026.96218076389</v>
       </c>
       <c r="B333" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>46019.33663729166</v>
+        <v>46026.96227592593</v>
       </c>
       <c r="B334" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>46019.34358173611</v>
+        <v>46026.96236971065</v>
       </c>
       <c r="B335" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>46019.35052618055</v>
+        <v>46026.96245789352</v>
       </c>
       <c r="B336" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
-        <v>46019.357470625</v>
+        <v>46026.96254366898</v>
       </c>
       <c r="B337" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>46019.36441506945</v>
+        <v>46026.96263072917</v>
       </c>
       <c r="B338" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>46019.37135951389</v>
+        <v>46026.96272608796</v>
       </c>
       <c r="B339" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
-        <v>46019.37830395834</v>
+        <v>46026.96283287037</v>
       </c>
       <c r="B340" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>46019.38524840278</v>
+        <v>46026.96292702547</v>
       </c>
       <c r="B341" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>46019.39219284722</v>
+        <v>46026.96302501157</v>
       </c>
       <c r="B342" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
-        <v>46019.39913729166</v>
+        <v>46026.96312460648</v>
       </c>
       <c r="B343" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>46019.40608173611</v>
+        <v>46026.9632162963</v>
       </c>
       <c r="B344" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>46019.41302618055</v>
+        <v>46026.96330564815</v>
       </c>
       <c r="B345" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>46019.419970625</v>
+        <v>46026.96535922454</v>
       </c>
       <c r="B346" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>46019.42691506945</v>
+        <v>46026.96545052083</v>
       </c>
       <c r="B347" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>46019.43385951389</v>
+        <v>46026.96555048611</v>
       </c>
       <c r="B348" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>46019.44080395834</v>
+        <v>46026.96564319445</v>
       </c>
       <c r="B349" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>46019.44774840278</v>
+        <v>46026.96573804398</v>
       </c>
       <c r="B350" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>46019.45469284722</v>
+        <v>46026.96583232639</v>
       </c>
       <c r="B351" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>46019.46163729166</v>
+        <v>46026.96592034723</v>
       </c>
       <c r="B352" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>46019.46858173611</v>
+        <v>46026.96600532407</v>
       </c>
       <c r="B353" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>46019.47552618055</v>
+        <v>46026.96609300926</v>
       </c>
       <c r="B354" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>46019.482470625</v>
+        <v>46026.966190625</v>
       </c>
       <c r="B355" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>46019.48941506945</v>
+        <v>46026.96632085648</v>
       </c>
       <c r="B356" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>46019.49635951389</v>
+        <v>46026.96641855324</v>
       </c>
       <c r="B357" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>46019.50330395834</v>
+        <v>46026.96652234954</v>
       </c>
       <c r="B358" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>46019.51024840278</v>
+        <v>46026.96662206019</v>
       </c>
       <c r="B359" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>46019.51719284722</v>
+        <v>46026.96671655092</v>
       </c>
       <c r="B360" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>46019.52413729166</v>
+        <v>46026.96681081018</v>
       </c>
       <c r="B361" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>46019.53108173611</v>
+        <v>46026.9683255787</v>
       </c>
       <c r="B362" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>46019.53802618055</v>
+        <v>46026.96841650463</v>
       </c>
       <c r="B363" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>46019.544970625</v>
+        <v>46026.96851987269</v>
       </c>
       <c r="B364" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>46019.55191506945</v>
+        <v>46026.96861547454</v>
       </c>
       <c r="B365" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>46019.55885951389</v>
+        <v>46026.96871075231</v>
       </c>
       <c r="B366" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>46019.56580395834</v>
+        <v>46026.96883153935</v>
       </c>
       <c r="B367" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>46019.57274840278</v>
+        <v>46026.96894686342</v>
       </c>
       <c r="B368" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>46019.57969284722</v>
+        <v>46026.96905525463</v>
       </c>
       <c r="B369" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>46019.58663729166</v>
+        <v>46026.9691712963</v>
       </c>
       <c r="B370" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>46019.59358173611</v>
+        <v>46026.96929592593</v>
       </c>
       <c r="B371" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>46019.60052618055</v>
+        <v>46026.96943689815</v>
       </c>
       <c r="B372" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>46019.607470625</v>
+        <v>46026.96956483796</v>
       </c>
       <c r="B373" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>46019.61441506945</v>
+        <v>46026.96969428241</v>
       </c>
       <c r="B374" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>46019.62135951389</v>
+        <v>46026.96979466435</v>
       </c>
       <c r="B375" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>46019.62830395834</v>
+        <v>46026.96988819444</v>
       </c>
       <c r="B376" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>46019.63524840278</v>
+        <v>46026.96998109954</v>
       </c>
       <c r="B377" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>46019.64219284722</v>
+        <v>46026.97060662037</v>
       </c>
       <c r="B378" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>46019.64913729166</v>
+        <v>46026.97082255787</v>
       </c>
       <c r="B379" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>46019.65608173611</v>
+        <v>46026.9710475</v>
       </c>
       <c r="B380" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>46019.66302618055</v>
+        <v>46026.9712734838</v>
       </c>
       <c r="B381" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>46019.669970625</v>
+        <v>46026.97148780093</v>
       </c>
       <c r="B382" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>46019.67691506945</v>
+        <v>46026.97170707176</v>
       </c>
       <c r="B383" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>46019.68385951389</v>
+        <v>46026.97192949074</v>
       </c>
       <c r="B384" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>46019.69080395834</v>
+        <v>46026.97290516204</v>
       </c>
       <c r="B385" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>46019.69774840278</v>
+        <v>46026.97312035879</v>
       </c>
       <c r="B386" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>46019.70469284722</v>
+        <v>46026.97334480324</v>
       </c>
       <c r="B387" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>46019.71163729166</v>
+        <v>46026.97356237269</v>
       </c>
       <c r="B388" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>46019.71858173611</v>
+        <v>46026.9738215625</v>
       </c>
       <c r="B389" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>46019.72552618055</v>
+        <v>46026.97406511574</v>
       </c>
       <c r="B390" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>46019.732470625</v>
+        <v>46026.97431615741</v>
       </c>
       <c r="B391" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>46019.73941506945</v>
+        <v>46026.9745953588</v>
       </c>
       <c r="B392" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>46019.74635951389</v>
+        <v>46026.97484729167</v>
       </c>
       <c r="B393" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>46019.75330395834</v>
+        <v>46026.97885400463</v>
       </c>
       <c r="B394" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>46019.76024840278</v>
+        <v>46026.97900916667</v>
       </c>
       <c r="B395" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>46019.76719284722</v>
+        <v>46026.97994912037</v>
       </c>
       <c r="B396" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>46019.77413729166</v>
+        <v>46026.98004197916</v>
       </c>
       <c r="B397" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>46019.78108173611</v>
+        <v>46026.98013928241</v>
       </c>
       <c r="B398" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>46019.78710940972</v>
+        <v>46026.98023246528</v>
       </c>
       <c r="B399" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>46019.78725230324</v>
+        <v>46026.98032490741</v>
       </c>
       <c r="B400" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>46019.78739605324</v>
+        <v>46026.98042162037</v>
       </c>
       <c r="B401" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>46019.78754708333</v>
+        <v>46026.98051215278</v>
       </c>
       <c r="B402" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>46019.78770908565</v>
+        <v>46026.98059828704</v>
       </c>
       <c r="B403" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>46019.7878722801</v>
+        <v>46026.98068773148</v>
       </c>
       <c r="B404" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>46019.78802618055</v>
+        <v>46026.98078954861</v>
       </c>
       <c r="B405" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>46019.78803903935</v>
+        <v>46026.98543059028</v>
       </c>
       <c r="B406" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>46019.78819797454</v>
+        <v>46026.98559810186</v>
       </c>
       <c r="B407" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>46019.78837785879</v>
+        <v>46026.98576128472</v>
       </c>
       <c r="B408" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>46019.78855489584</v>
+        <v>46026.9859168287</v>
       </c>
       <c r="B409" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>46019.788728125</v>
+        <v>46026.98607233796</v>
       </c>
       <c r="B410" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>46019.78890439815</v>
+        <v>46026.98664226852</v>
       </c>
       <c r="B411" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>46019.78909473379</v>
+        <v>46026.9867378588</v>
       </c>
       <c r="B412" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>46019.78927900463</v>
+        <v>46026.98684487268</v>
       </c>
       <c r="B413" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>46019.78945652777</v>
+        <v>46026.9869387963</v>
       </c>
       <c r="B414" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>46019.78962299768</v>
+        <v>46026.98703403935</v>
       </c>
       <c r="B415" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>46019.794970625</v>
+        <v>46026.98713006944</v>
       </c>
       <c r="B416" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>46019.79917954861</v>
+        <v>46026.98721981482</v>
       </c>
       <c r="B417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>46019.79933003472</v>
+        <v>46026.98731056713</v>
       </c>
       <c r="B418" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>46019.79948458333</v>
+        <v>46026.98740233796</v>
       </c>
       <c r="B419" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>46019.79964241898</v>
+        <v>46026.98750497685</v>
       </c>
       <c r="B420" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>46019.79980773148</v>
+        <v>46026.98761710648</v>
       </c>
       <c r="B421" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>46019.79997678241</v>
+        <v>46026.98771641203</v>
       </c>
       <c r="B422" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>46019.80014923611</v>
+        <v>46026.98781721065</v>
       </c>
       <c r="B423" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>46019.80032202546</v>
+        <v>46026.98791956018</v>
       </c>
       <c r="B424" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>46019.80050456018</v>
+        <v>46026.98801528935</v>
       </c>
       <c r="B425" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>46019.80069651621</v>
+        <v>46026.98810939815</v>
       </c>
       <c r="B426" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>46019.80088616898</v>
+        <v>46026.99216025463</v>
       </c>
       <c r="B427" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>46019.80106292824</v>
+        <v>46026.99232880787</v>
       </c>
       <c r="B428" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>46019.80124872685</v>
+        <v>46026.99249574074</v>
       </c>
       <c r="B429" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>46019.80143684028</v>
+        <v>46026.99265369213</v>
       </c>
       <c r="B430" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>46019.80161681713</v>
+        <v>46026.99280633102</v>
       </c>
       <c r="B431" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>46019.8017946412</v>
+        <v>46026.99296239583</v>
       </c>
       <c r="B432" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>46019.80191506945</v>
+        <v>46026.99312706019</v>
       </c>
       <c r="B433" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>46019.80630458333</v>
+        <v>46026.99328833333</v>
       </c>
       <c r="B434" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>46019.80639174768</v>
+        <v>46026.99346690972</v>
       </c>
       <c r="B435" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>46019.80648799769</v>
+        <v>46026.99364174769</v>
       </c>
       <c r="B436" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>46019.80657899306</v>
+        <v>46026.99381905093</v>
       </c>
       <c r="B437" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>46019.80667068287</v>
+        <v>46026.99399303241</v>
       </c>
       <c r="B438" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>46019.8067622338</v>
+        <v>46026.99418137731</v>
       </c>
       <c r="B439" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>46019.80685096065</v>
+        <v>46026.99435589121</v>
       </c>
       <c r="B440" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>46019.80694037037</v>
+        <v>46026.99452862269</v>
       </c>
       <c r="B441" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>46019.80702836806</v>
+        <v>46026.99468518519</v>
       </c>
       <c r="B442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>46019.80712328704</v>
+        <v>46026.99484137732</v>
       </c>
       <c r="B443" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>46019.80722640047</v>
+        <v>46026.9950215162</v>
       </c>
       <c r="B444" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>46019.80732671297</v>
+        <v>46026.99521114583</v>
       </c>
       <c r="B445" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>46019.80742377315</v>
+        <v>46026.99542152778</v>
       </c>
       <c r="B446" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>46019.8671515625</v>
+        <v>46026.99561201389</v>
       </c>
       <c r="B447" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>46019.86730526621</v>
+        <v>46026.99578751157</v>
       </c>
       <c r="B448" t="n">
         <v>7</v>
@@ -4022,39 +4022,39 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>46019.86745759259</v>
+        <v>46026.99597653935</v>
       </c>
       <c r="B449" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>46019.86760027778</v>
+        <v>46026.99616233796</v>
       </c>
       <c r="B450" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>46019.86774581019</v>
+        <v>46026.9963484375</v>
       </c>
       <c r="B451" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>46019.86789157407</v>
+        <v>46026.99657451389</v>
       </c>
       <c r="B452" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>46019.86804280092</v>
+        <v>46026.99678642361</v>
       </c>
       <c r="B453" t="n">
         <v>6</v>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>46019.86819030093</v>
+        <v>46026.99699333333</v>
       </c>
       <c r="B454" t="n">
         <v>6</v>
@@ -4070,31 +4070,31 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>46019.86834508102</v>
+        <v>46026.99721868055</v>
       </c>
       <c r="B455" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>46019.86854447917</v>
+        <v>46026.99739804398</v>
       </c>
       <c r="B456" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>46019.86981938657</v>
+        <v>46026.99757733796</v>
       </c>
       <c r="B457" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>46019.87001287037</v>
+        <v>46026.99812849537</v>
       </c>
       <c r="B458" t="n">
         <v>6</v>
@@ -4102,223 +4102,223 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>46019.87890775463</v>
+        <v>46026.99829215278</v>
       </c>
       <c r="B459" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>46019.87906486111</v>
+        <v>46026.9984577662</v>
       </c>
       <c r="B460" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>46019.87922371528</v>
+        <v>46026.99862526621</v>
       </c>
       <c r="B461" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>46019.87936680556</v>
+        <v>46026.99880790509</v>
       </c>
       <c r="B462" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>46019.87950716435</v>
+        <v>46026.99899054398</v>
       </c>
       <c r="B463" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>46019.87965185185</v>
+        <v>46026.99915973379</v>
       </c>
       <c r="B464" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>46019.87980674768</v>
+        <v>46026.99934876157</v>
       </c>
       <c r="B465" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>46019.87996484954</v>
+        <v>46026.99955096065</v>
       </c>
       <c r="B466" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>46019.88012774305</v>
+        <v>46026.99975504629</v>
       </c>
       <c r="B467" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>46019.90720983796</v>
+        <v>46026.99995222222</v>
       </c>
       <c r="B468" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>46019.90729984954</v>
+        <v>46027.00019599537</v>
       </c>
       <c r="B469" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>46019.90739475694</v>
+        <v>46027.00043023148</v>
       </c>
       <c r="B470" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>46019.9074912037</v>
+        <v>46027.00066231481</v>
       </c>
       <c r="B471" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>46019.90758472222</v>
+        <v>46027.00090648148</v>
       </c>
       <c r="B472" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>46019.90768146991</v>
+        <v>46027.00114631945</v>
       </c>
       <c r="B473" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>46019.90777574074</v>
+        <v>46027.0033874537</v>
       </c>
       <c r="B474" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>46019.90787814815</v>
+        <v>46027.00355410879</v>
       </c>
       <c r="B475" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>46019.90797552084</v>
+        <v>46027.00371666667</v>
       </c>
       <c r="B476" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>46019.90807</v>
+        <v>46027.00388277778</v>
       </c>
       <c r="B477" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>46019.90816299769</v>
+        <v>46027.00406226852</v>
       </c>
       <c r="B478" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>46019.90827078704</v>
+        <v>46027.00424325231</v>
       </c>
       <c r="B479" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>46019.9083687963</v>
+        <v>46027.00442530093</v>
       </c>
       <c r="B480" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>46019.90847293982</v>
+        <v>46027.00460480324</v>
       </c>
       <c r="B481" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>46019.9085774074</v>
+        <v>46027.00480506945</v>
       </c>
       <c r="B482" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>46019.90868396991</v>
+        <v>46027.00500984953</v>
       </c>
       <c r="B483" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>46019.90879077547</v>
+        <v>46027.00520998843</v>
       </c>
       <c r="B484" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>46019.90888137731</v>
+        <v>46027.00541092593</v>
       </c>
       <c r="B485" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>46020.39276376157</v>
+        <v>46027.00610326389</v>
       </c>
       <c r="B486" t="n">
         <v>6</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>46020.39292097222</v>
+        <v>46027.0062674537</v>
       </c>
       <c r="B487" t="n">
         <v>5</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>46020.39307635416</v>
+        <v>46027.00642944445</v>
       </c>
       <c r="B488" t="n">
         <v>5</v>
@@ -4342,7 +4342,7 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>46020.39323398148</v>
+        <v>46027.00659909722</v>
       </c>
       <c r="B489" t="n">
         <v>4</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>46020.39341068287</v>
+        <v>46027.00677782408</v>
       </c>
       <c r="B490" t="n">
         <v>8</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>46020.39359583333</v>
+        <v>46027.00695902778</v>
       </c>
       <c r="B491" t="n">
         <v>6</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>46020.39377560185</v>
+        <v>46027.00714033565</v>
       </c>
       <c r="B492" t="n">
         <v>8</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>46020.39395383102</v>
+        <v>46027.00732089121</v>
       </c>
       <c r="B493" t="n">
         <v>9</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>46020.39413903935</v>
+        <v>46027.00751410879</v>
       </c>
       <c r="B494" t="n">
         <v>13</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>46020.39432732639</v>
+        <v>46027.00771929398</v>
       </c>
       <c r="B495" t="n">
         <v>9</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>46020.39451603009</v>
+        <v>46027.00791979166</v>
       </c>
       <c r="B496" t="n">
         <v>11</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>46020.39471405093</v>
+        <v>46027.00811762732</v>
       </c>
       <c r="B497" t="n">
         <v>12</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>46020.39490146991</v>
+        <v>46027.00831135417</v>
       </c>
       <c r="B498" t="n">
         <v>11</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>46020.39510195602</v>
+        <v>46027.00850170139</v>
       </c>
       <c r="B499" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>46020.39528770834</v>
+        <v>46027.00868260417</v>
       </c>
       <c r="B500" t="n">
         <v>9</v>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>46020.39546400463</v>
+        <v>46027.00886069444</v>
       </c>
       <c r="B501" t="n">
         <v>12</v>
